--- a/Config/GameConfig.xlsx
+++ b/Config/GameConfig.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
   <si>
     <t xml:space="preserve">Id</t>
   </si>
@@ -636,6 +636,30 @@
   </si>
   <si>
     <t xml:space="preserve">敌人伤害每波倍率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArenaHalfExtent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">玩家可达区域的半边长 米</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DashSpeedMultiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冲刺速度是移速的倍数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DashDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冲刺持续 秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DashCooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冲刺冷却 秒</t>
   </si>
 </sst>
 </file>
@@ -2027,6 +2051,50 @@
         <v>206</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9">
+        <v>3.0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10">
+        <v>0.15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11">
+        <v>2.0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>214</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>